--- a/Paket_6_Bahasa_Indonesia_TKA_SD.xlsx
+++ b/Paket_6_Bahasa_Indonesia_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 6 Bahasa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 1: contoh soal pemahaman teks.</t>
+          <t>Bacalah paragraf berikut dengan cermat! 'Pagi hari di Dusun Sukamaju selalu dipenuhi kesibukan warga. Sebelum matahari beranjak tinggi, Pak Tono sudah berjalan kaki menuju sawah membentang di kaki bukit sambil membawa cangkul di pundaknya. Sementara itu, istrinya, Bu Siti, menyiapkan sarapan hangat dan menyiram tanaman obat di halaman rumah.' Pernyataan manakah yang sesuai dengan isi paragraf tersebut?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Pak Tono pergi ke sawah bersama istrinya membawa cangkul</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Bu Siti menyiapkan sarapan hangat dan menyiram tanaman obat</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Warga Dusun Sukamaju bekerja di sawah menjelang sore hari</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Pak Tono dan Bu Siti tinggal di daerah perkotaan yang padat</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 2: contoh soal pemahaman teks.</t>
+          <t>Bacalah teks berikut! 'Sampah plastik merupakan salah satu permasalahan lingkungan yang sangat serius di era modern saat ini. Sifatnya yang sangat sulit terurai secara alami menyebabkan sampah plastik menumpuk di tanah dan mencemari ekosistem laut. Jika tidak segera ditangani dengan bijak melalui daur ulang dan pembatasan penggunaan, sampah plastik akan mengancam kelangsungan hidup satwa bumi.' Ide pokok paragraf tersebut adalah...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Pentingnya melakukan daur ulang sampah plastik di kota besar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Dampak buruk dan ancaman serius dari permasalahan sampah plastik</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Cara mudah menguraikan sampah plastik di dalam tanah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Kehidupan satwa di darat dan laut yang terganggu oleh limbah industri</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 3: contoh soal pemahaman teks.</t>
+          <t>Bacalah kalimat berikut! 'Pemerintah melalui dinas terkait gencar melakukan sosialisasi tentang pentingnya menjaga kesehatan gigi kepada para siswa sekolah dasar.' Apakah makna kata sosialisasi dalam kalimat tersebut?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Pemberian bantuan fasilitas kesehatan dan obat gratis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Upaya penyuluhan atau pengenalan agar masyarakat paham dan mengerti</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Pelaksanaan pemeriksaan medis secara massal di sekolah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Peraturan ketat tentang kebersihan lingkungan sekolah</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 4: contoh soal pemahaman teks.</t>
+          <t>Bacalah pantun berikut! Pergi ke kebun memetik tomat, Jangan lupa membawa keranjang. Jika kamu rajin berhemat, Masa depan pasti kan gemilang. Pesan atau amanat yang terkandung dalam pantun tersebut adalah...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Kita harus rajin memetik buah tomat di kebun</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Membawa keranjang sangat penting saat berkebun</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Kebiasaan hidup rajin berhemat akan mengantarkan pada kesuksesan di masa depan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Masa depan yang gemilang hanya milik orang kaya</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,17 +637,21 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 5: contoh soal pemahaman teks.</t>
+          <t>Bacalah kutipan cerita anak berikut! 'Setiap sore, Dimas selalu menyempatkan diri mengajari Rian membaca di teras rumahnya tanpa meminta imbalan sedikit pun. Walaupun Rian sering kesulitan memahami huruf, Dimas tidak pernah marah atau membentak.' Manakah pernyataan yang BENAR mengenai sifat dan unsur cerita tersebut? (Jawaban benar lebih dari satu) ☐ A. Tokoh Dimas memiliki watak yang sabar dan suka menolong ☐ B. Tokoh Rian digambarkan sebagai anak yang mudah menyerah dan pemarah ☐ C. Latar tempat kejadian dalam kutipan cerita tersebut adalah di teras rumah ☐ D. Amanat cerita adalah kita hendaknya saling membantu sesama dengan ketulusan hati [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -666,7 +682,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +696,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 6: contoh soal pemahaman teks.</t>
+          <t>Bacalah kalimat rumpang berikut! 'Pihak sekolah mengimbau para orang tua siswa agar melakukan (...) ulang daftar ulang secara mandiri melalui laman web resmi.' Kata baku yang tepat untuk melengkapi bagian rumpang kalimat tersebut adalah...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. konfirmasi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. konfirmasi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. konfirmasi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. konfirmasi</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,17 +727,21 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 7: contoh soal pemahaman teks.</t>
+          <t>Bacalah teks informasi kesehatan berikut! 'Vitamin C sangat penting untuk menjaga daya tahan tubuh manusia. Buah-buahan segar seperti jeruk, jambu biji, kiwi, dan pepaya merupakan sumber vitamin C alami yang sangat baik. Kekurangan vitamin C dapat memicu sariawan, gusi berdarah, dan kelelahan kronis.' Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,7 +772,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +786,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 8: contoh soal pemahaman teks.</t>
+          <t>Bacalah kalimat berikut! 'Keputusan ketua kelompok dalam menyelesaikan perselisihan antaranggota dinilai sangat bijaksana.' Sinonim dari kata 'bijaksana' dalam kalimat tersebut adalah...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. adil dan arif</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. tegas dan keras</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. cepat dan tanggap</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. pandai dan cerdik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +817,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +831,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 9: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat-kalimat acak petunjuk membuat kerajinan berikut! (1) Potonglah botol plastik bekas menjadi dua bagian sama panjang. (2) Bersihkan botol plastik dari sisa label dan kotoran menggunakan air bersih. (3) Hiasi badan botol menggunakan cat akrilik dan pita warna-warni. (4) Lubangi bagian bawah botol dengan paku panas untuk sirkulasi air tanaman. Urutan petunjuk pembuatan pot bunga gantung dari botol bekas yang padu adalah...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. (2) - (1) - (4) - (3)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. (2) - (3) - (1) - (4)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. (1) - (2) - (3) - (4)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. (2) - (1) - (3) - (4)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +862,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +876,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 10: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat berikut! 'bibi membeli 3 kg mangga arumanis di pasar induk surabaya pada hari minggu.' Perbaikan penulisan huruf kapital dan tanda baca yang tepat pada kalimat tersebut adalah...</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Bibi membeli 3 kg mangga arumanis di Pasar Induk Surabaya pada hari Minggu.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Bibi membeli 3 kg Mangga Arumanis di pasar induk Surabaya pada Hari Minggu.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. bibi membeli 3 kg mangga arumanis di Pasar Induk Surabaya pada hari minggu.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Bibi Membeli 3 kg mangga arumanis di Pasar Induk Surabaya Pada Hari Minggu.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +907,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +921,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 11: contoh soal pemahaman teks.</t>
+          <t>Bacalah teks eksplanasi ilmiah berikut! 'Pembangkit Listrik Tenaga Mikrohidro (PLTMH) memanfaatkan aliran air sungai kecil untuk memutar turbin. Perputaran turbin tersebut menggerakkan generator yang kemudian menghasilkan energi listrik ramah lingkungan bagi warga perkampungan.' Informasi tersurat yang sesuai dengan teks tersebut adalah...</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. PLTMH menggunakan tenaga angin kencang untuk memutar turbin generator</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Aliran air sungai kecil dimanfaatkan untuk memutar turbin penghasil listrik</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Energi listrik dari PLTMH disalurkan khusus untuk pabrik industri besar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Generator tidak dibutuhkan dalam sistem operasional Pembangkit Listrik Mikrohidro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,17 +952,21 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 12: contoh soal pemahaman teks.</t>
+          <t>Bacalah ilustrasi cerita berikut! 'Sejak kedai kopi miliknya sepi pengunjung akibat persaingan ketat, Pak Harun tidak pernah patah semangat. Beliau terus memutar otak mencari inovasi menu baru dan memberikan pelayanan ramah kepada setiap pembeli.' Manakah ungkapan atau peribahasa yang SESUAI dengan ilustrasi cerita tersebut? (Jawaban benar lebih dari satu) ☐ A. Ungkapan 'putar otak' bermakna berpikir keras untuk mencari jalan keluar ☐ B. Peribahasa 'berat sama dipikul, ringan sama dijinjing' sesuai dengan kisah Pak Harun ☐ C. Sikap Pak Harun mencerminkan kegigihan dan pantang menyerah dalam berwirausaha ☐ D. Ungkapan 'banting tulang' juga menggambarkan kerja keras yang dilakukan Pak Harun [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -953,7 +997,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 13: contoh soal pemahaman teks.</t>
+          <t>Bacalah paragraf berikut! '(1) Buku merupakan jendela dunia yang memberikan banyak pengetahuan berharga bagi pembacanya. (2) Dengan membaca buku, wawasan kita tentang berbagai ilmu pengetahuan akan semakin luas. (3) Selain itu, kebiasaan membaca juga mampu melatih daya konsentrasi dan kemampuan berpikir kritis. (4) Oleh sebab itu, minat baca anak-anak harus ditanamkan sejak usia dini.' Kalimat utama paragraf tersebut terdapat pada nomor...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. (1)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. (2)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. (3)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. (4)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1042,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,7 +1056,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 14: contoh soal pemahaman teks.</t>
+          <t>Perhatikan data isian formulir pendaftaran anggota perpustakaan berikut:</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1035,7 +1087,11 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1045,7 +1101,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 15: contoh soal pemahaman teks.</t>
+          <t>Nama Lengkap: Salsabila Putri</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1132,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,7 +1146,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 16: contoh soal pemahaman teks.</t>
+          <t>Tempat, Tanggal Lahir: Bandung, 14 Mei 2015</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1117,7 +1177,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,7 +1191,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 17: contoh soal pemahaman teks.</t>
+          <t>Alamat: Jalan Melati Nomor 12, Cimahi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1158,7 +1222,11 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1168,27 +1236,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 18: contoh soal pemahaman teks.</t>
+          <t>Sekolah: SD Tunas Bangsa Jika Salsabila ingin meminjam buku paket perpustakaan, bagian data manakah yang menunjukkan identitas sekolahnya...</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Nomor 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Nomor 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Nomor 3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Nomor 4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,17 +1267,21 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 19: contoh soal pemahaman teks.</t>
+          <t>Bacalah teks ulasan buku berikut! 'Buku berjudul "Petualangan di Hutan Rimba" karya Kak Ardi sangat menarik dibaca oleh anak-anak usia sekolah dasar. Alur cerita penuh misteri dan pesan moral tentang kepedulian lingkungan disampaikan dengan bahasa yang sangat komunikatif dan ilustrasi gambar berwarna yang memukau.' Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1240,7 +1312,11 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1250,27 +1326,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Bahasa 20: contoh soal pemahaman teks.</t>
+          <t>Bacalah kutipan fabel berikut! 'Di tepi sebuah sungai yang jernih, Kancil sedang menikmati rerimbunan rumput muda. Tiba-tiba, Kancil mendengar suara rintihan kesakitan dari arah semak belukar. Tanpa pikir panjang, Kancil segera melompat mendekati sumber suara untuk memberikan pertolongan.' Sifat tokoh Kancil dalam kutipan fabel tersebut adalah...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. sombong dan cerdik</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. suka menolong dan peduli</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. pemarah dan penakut</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. pemalu dan pendiam</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1281,7 +1357,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
